--- a/test/session--empty-statements/reference/2 semester 14 subjects/II семестр/25-2/Відомості 25-2.xlsx
+++ b/test/session--empty-statements/reference/2 semester 14 subjects/II семестр/25-2/Відомості 25-2.xlsx
@@ -27,7 +27,7 @@
     <definedName name="Ф80" localSheetId="3">#REF!</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Зведена G16'!$C$3:$S$34</definedName>
   </definedNames>
-  <calcPr calcId="191029" calcMode="autoNoTable" fullCalcOnLoad="1"/>
+  <calcPr calcId="152511" calcMode="autoNoTable" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -3114,7 +3114,7 @@
         </is>
       </c>
       <c r="F53" s="63">
-        <f>IF(F50="Очікую","Очікую",IF(F50-COUNTIF($T$10:$T44," - ")&lt;ROUNDDOWN(F50*0.4,0),F50-COUNTIF($T$10:$T44," - "),ROUNDDOWN(F50*0.4,0)))</f>
+        <f>IF(F50="Очікую","Очікую",IF(F50-COUNTIF($T$10:$T44," - ")&lt;ROUNDDOWN(F50*0.45,0),F50-COUNTIF($T$10:$T44," - "),ROUNDDOWN(F50*0.45,0)))</f>
         <v/>
       </c>
       <c r="G53" s="6" t="n"/>
@@ -3132,7 +3132,7 @@
       <c r="O53" s="54" t="n"/>
       <c r="P53" s="54" t="inlineStr">
         <is>
-          <t>Margarita BRITIKOVA</t>
+          <t>Маргарита БРІТІКОВА</t>
         </is>
       </c>
       <c r="Q53" s="54" t="n"/>
@@ -3416,7 +3416,7 @@
       <c r="B5" s="12" t="n"/>
       <c r="C5" s="73" t="inlineStr">
         <is>
-          <t>Успішності студентів спеціальності D7 ««Торгівля»»</t>
+          <t>Успішності студентів спеціальності D7 «Торгівля»</t>
         </is>
       </c>
       <c r="D5" s="92" t="n"/>
@@ -5144,7 +5144,7 @@
         </is>
       </c>
       <c r="F33" s="63">
-        <f>IF(F30="Очікую","Очікую",IF(F30-COUNTIF($T$10:$T24," - ")&lt;ROUNDDOWN(F30*0.4,0),F30-COUNTIF($T$10:$T24," - "),ROUNDDOWN(F30*0.4,0)))</f>
+        <f>IF(F30="Очікую","Очікую",IF(F30-COUNTIF($T$10:$T24," - ")&lt;ROUNDDOWN(F30*0.45,0),F30-COUNTIF($T$10:$T24," - "),ROUNDDOWN(F30*0.45,0)))</f>
         <v/>
       </c>
       <c r="G33" s="6" t="n"/>
@@ -5162,7 +5162,7 @@
       <c r="O33" s="56" t="n"/>
       <c r="P33" s="54" t="inlineStr">
         <is>
-          <t>Margarita BRITIKOVA</t>
+          <t>Маргарита БРІТІКОВА</t>
         </is>
       </c>
       <c r="Q33" s="54" t="n"/>
@@ -5470,7 +5470,7 @@
       <c r="B5" s="12" t="n"/>
       <c r="C5" s="73" t="inlineStr">
         <is>
-          <t>Успішності студентів спеціальності G1 ««Хімічні технології та інженерія»»</t>
+          <t>Успішності студентів спеціальності G1 «Хімічні технології та інженерія»</t>
         </is>
       </c>
       <c r="D5" s="92" t="n"/>
@@ -6351,7 +6351,7 @@
         </is>
       </c>
       <c r="F22" s="63">
-        <f>IF(F19="Очікую","Очікую",IF(F19-COUNTIF($T$10:$T13," - ")&lt;ROUNDDOWN(F19*0.4,0),F19-COUNTIF($T$10:$T13," - "),ROUNDDOWN(F19*0.4,0)))</f>
+        <f>IF(F19="Очікую","Очікую",IF(F19-COUNTIF($T$10:$T13," - ")&lt;ROUNDDOWN(F19*0.45,0),F19-COUNTIF($T$10:$T13," - "),ROUNDDOWN(F19*0.45,0)))</f>
         <v/>
       </c>
       <c r="G22" s="6" t="n"/>
@@ -6369,7 +6369,7 @@
       <c r="O22" s="56" t="n"/>
       <c r="P22" s="54" t="inlineStr">
         <is>
-          <t>Margarita BRITIKOVA</t>
+          <t>Маргарита БРІТІКОВА</t>
         </is>
       </c>
       <c r="Q22" s="54" t="n"/>
@@ -6688,7 +6688,7 @@
       <c r="B5" s="12" t="n"/>
       <c r="C5" s="73" t="inlineStr">
         <is>
-          <t>Успішності студентів спеціальності G16 ««Гірництво та нафтогазові технології»»</t>
+          <t>Успішності студентів спеціальності G16 «Гірництво та нафтогазові технології»</t>
         </is>
       </c>
       <c r="D5" s="92" t="n"/>
@@ -8493,7 +8493,7 @@
         </is>
       </c>
       <c r="F34" s="63">
-        <f>IF(F31="Очікую","Очікую",IF(F31-COUNTIF($T$10:$T25," - ")&lt;ROUNDDOWN(F31*0.4,0),F31-COUNTIF($T$10:$T25," - "),ROUNDDOWN(F31*0.4,0)))</f>
+        <f>IF(F31="Очікую","Очікую",IF(F31-COUNTIF($T$10:$T25," - ")&lt;ROUNDDOWN(F31*0.45,0),F31-COUNTIF($T$10:$T25," - "),ROUNDDOWN(F31*0.45,0)))</f>
         <v/>
       </c>
       <c r="G34" s="6" t="n"/>
@@ -8511,7 +8511,7 @@
       <c r="O34" s="56" t="n"/>
       <c r="P34" s="54" t="inlineStr">
         <is>
-          <t>Margarita BRITIKOVA</t>
+          <t>Маргарита БРІТІКОВА</t>
         </is>
       </c>
       <c r="Q34" s="54" t="n"/>
